--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrInvestAllInfoPB.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrInvestAllInfoPB.xlsx
@@ -1,31 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15" conformance="strict">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr dateCompatibility="0" checkCompatibility="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23628"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\tams-3.0\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1A92897-7077-469B-A6C5-51E2CA5C943C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19170" windowHeight="8400"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="说明" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
-      <x14:workbookPr/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>交易市场(必填)</t>
   </si>
@@ -78,7 +74,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.000_);[Red]\(0.000\)"/>
   </numFmts>
@@ -120,19 +116,19 @@
   </fills>
   <borders count="2">
     <border>
-      <start/>
-      <end/>
+      <left/>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <start style="thin">
+      <left style="thin">
         <color rgb="FF000000"/>
-      </start>
-      <end style="thin">
+      </left>
+      <right style="thin">
         <color rgb="FF000000"/>
-      </end>
+      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -147,27 +143,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -193,7 +180,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -209,13 +196,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1039" name="图片 1"/>
+        <xdr:cNvPr id="1039" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000F040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -252,7 +245,7 @@
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:miter lim="800%"/>
+              <a:miter lim="800000"/>
               <a:headEnd/>
               <a:tailEnd/>
             </a14:hiddenLine>
@@ -277,13 +270,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1040" name="图片 3"/>
+        <xdr:cNvPr id="1040" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000010040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -320,7 +319,7 @@
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:miter lim="800%"/>
+              <a:miter lim="800000"/>
               <a:headEnd/>
               <a:tailEnd/>
             </a14:hiddenLine>
@@ -345,13 +344,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1041" name="图片 4"/>
+        <xdr:cNvPr id="1041" name="图片 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000011040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" r:embed="rId3">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -388,7 +393,7 @@
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:miter lim="800%"/>
+              <a:miter lim="800000"/>
               <a:headEnd/>
               <a:tailEnd/>
             </a14:hiddenLine>
@@ -413,13 +418,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1042" name="图片 5"/>
+        <xdr:cNvPr id="1042" name="图片 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000012040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" r:embed="rId4">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -456,7 +467,7 @@
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:miter lim="800%"/>
+              <a:miter lim="800000"/>
               <a:headEnd/>
               <a:tailEnd/>
             </a14:hiddenLine>
@@ -470,7 +481,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -589,25 +600,25 @@
         </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0%">
+            <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110%"/>
-                <a:satMod val="105%"/>
-                <a:tint val="67%"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50%">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105%"/>
-                <a:satMod val="103%"/>
-                <a:tint val="73%"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="100%">
+            <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105%"/>
-                <a:satMod val="109%"/>
-                <a:tint val="81%"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -615,25 +626,25 @@
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0%">
+            <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103%"/>
-                <a:lumMod val="102%"/>
-                <a:tint val="94%"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50%">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110%"/>
-                <a:lumMod val="100%"/>
-                <a:shade val="100%"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="100%">
+            <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99%"/>
-                <a:satMod val="120%"/>
-                <a:shade val="78%"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -646,21 +657,21 @@
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800%"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800%"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800%"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -674,7 +685,7 @@
           <a:effectLst>
             <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63%"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -686,32 +697,32 @@
         </a:solidFill>
         <a:solidFill>
           <a:schemeClr val="phClr">
-            <a:tint val="95%"/>
-            <a:satMod val="170%"/>
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0%">
+            <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93%"/>
-                <a:satMod val="150%"/>
-                <a:shade val="98%"/>
-                <a:lumMod val="102%"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50%">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="98%"/>
-                <a:satMod val="130%"/>
-                <a:shade val="90%"/>
-                <a:lumMod val="103%"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="100%">
+            <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63%"/>
-                <a:satMod val="120%"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -731,2099 +742,2084 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P673"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="15.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="15.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="19.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="4" width="15.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="15.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="18" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="19" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="20" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="21" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="22" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="23" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="24" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="25" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="26" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="27" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E27" s="2"/>
     </row>
-    <row r="28" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="28" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="29" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="30" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="31" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E31" s="2"/>
     </row>
-    <row r="32" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="32" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E32" s="2"/>
     </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="33" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E33" s="2"/>
     </row>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="34" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E34" s="2"/>
     </row>
-    <row r="35" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="35" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E35" s="2"/>
     </row>
-    <row r="36" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="36" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E36" s="2"/>
     </row>
-    <row r="37" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="37" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E37" s="2"/>
     </row>
-    <row r="38" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="38" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E38" s="2"/>
     </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="39" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E39" s="2"/>
     </row>
-    <row r="40" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="40" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E40" s="2"/>
     </row>
-    <row r="41" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="41" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E41" s="2"/>
     </row>
-    <row r="42" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="42" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E42" s="2"/>
     </row>
-    <row r="43" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="43" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E43" s="2"/>
     </row>
-    <row r="44" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="44" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E44" s="2"/>
     </row>
-    <row r="45" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="45" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E45" s="2"/>
     </row>
-    <row r="46" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="46" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E46" s="2"/>
     </row>
-    <row r="47" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="47" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E47" s="2"/>
     </row>
-    <row r="48" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="48" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E48" s="2"/>
     </row>
-    <row r="49" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="49" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E49" s="2"/>
     </row>
-    <row r="50" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="50" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E50" s="2"/>
     </row>
-    <row r="51" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="51" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E51" s="2"/>
     </row>
-    <row r="52" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="52" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E52" s="2"/>
     </row>
-    <row r="53" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="53" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E53" s="2"/>
     </row>
-    <row r="54" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="54" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E54" s="2"/>
     </row>
-    <row r="55" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="55" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E55" s="2"/>
     </row>
-    <row r="56" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="56" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E56" s="2"/>
     </row>
-    <row r="57" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="57" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E57" s="2"/>
     </row>
-    <row r="58" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="58" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E58" s="2"/>
     </row>
-    <row r="59" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="59" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E59" s="2"/>
     </row>
-    <row r="60" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="60" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E60" s="2"/>
     </row>
-    <row r="61" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="61" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E61" s="2"/>
     </row>
-    <row r="62" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="62" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E62" s="2"/>
     </row>
-    <row r="63" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="63" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E63" s="2"/>
     </row>
-    <row r="64" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="64" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E64" s="2"/>
     </row>
-    <row r="65" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="65" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E65" s="2"/>
     </row>
-    <row r="66" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="66" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E66" s="2"/>
     </row>
-    <row r="67" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="67" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E67" s="2"/>
     </row>
-    <row r="68" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="68" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E68" s="2"/>
     </row>
-    <row r="69" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="69" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E69" s="2"/>
     </row>
-    <row r="70" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="70" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E70" s="2"/>
     </row>
-    <row r="71" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="71" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E71" s="2"/>
     </row>
-    <row r="72" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="72" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E72" s="2"/>
     </row>
-    <row r="73" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="73" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E73" s="2"/>
     </row>
-    <row r="74" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="74" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E74" s="2"/>
     </row>
-    <row r="75" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="75" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E75" s="2"/>
     </row>
-    <row r="76" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="76" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E76" s="2"/>
     </row>
-    <row r="77" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="77" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E77" s="2"/>
     </row>
-    <row r="78" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="78" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E78" s="2"/>
     </row>
-    <row r="79" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="79" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E79" s="2"/>
     </row>
-    <row r="80" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="80" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E80" s="2"/>
     </row>
-    <row r="81" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="81" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E81" s="2"/>
     </row>
-    <row r="82" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="82" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E82" s="2"/>
     </row>
-    <row r="83" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="83" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E83" s="2"/>
     </row>
-    <row r="84" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="84" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E84" s="2"/>
     </row>
-    <row r="85" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="85" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E85" s="2"/>
     </row>
-    <row r="86" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="86" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E86" s="2"/>
     </row>
-    <row r="87" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="87" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E87" s="2"/>
     </row>
-    <row r="88" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="88" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E88" s="2"/>
     </row>
-    <row r="89" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="89" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E89" s="2"/>
     </row>
-    <row r="90" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="90" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E90" s="2"/>
     </row>
-    <row r="91" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="91" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E91" s="2"/>
     </row>
-    <row r="92" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="92" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E92" s="2"/>
     </row>
-    <row r="93" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="93" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E93" s="2"/>
     </row>
-    <row r="94" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="94" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E94" s="2"/>
     </row>
-    <row r="95" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="95" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E95" s="2"/>
     </row>
-    <row r="96" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="96" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E96" s="2"/>
     </row>
-    <row r="97" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="97" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E97" s="2"/>
     </row>
-    <row r="98" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="98" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E98" s="2"/>
     </row>
-    <row r="99" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="99" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E99" s="2"/>
     </row>
-    <row r="100" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="100" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E100" s="2"/>
     </row>
-    <row r="101" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="101" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E101" s="2"/>
     </row>
-    <row r="102" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="102" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E102" s="2"/>
     </row>
-    <row r="103" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="103" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E103" s="2"/>
     </row>
-    <row r="104" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="104" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E104" s="2"/>
     </row>
-    <row r="105" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="105" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E105" s="2"/>
     </row>
-    <row r="106" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="106" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E106" s="2"/>
     </row>
-    <row r="107" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="107" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E107" s="2"/>
     </row>
-    <row r="108" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="108" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E108" s="2"/>
     </row>
-    <row r="109" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="109" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E109" s="2"/>
     </row>
-    <row r="110" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="110" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E110" s="2"/>
     </row>
-    <row r="111" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="111" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E111" s="2"/>
     </row>
-    <row r="112" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="112" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E112" s="2"/>
     </row>
-    <row r="113" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="113" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E113" s="2"/>
     </row>
-    <row r="114" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="114" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E114" s="2"/>
     </row>
-    <row r="115" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="115" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E115" s="2"/>
     </row>
-    <row r="116" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="116" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E116" s="2"/>
     </row>
-    <row r="117" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="117" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E117" s="2"/>
     </row>
-    <row r="118" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="118" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E118" s="2"/>
     </row>
-    <row r="119" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="119" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E119" s="2"/>
     </row>
-    <row r="120" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="120" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E120" s="2"/>
     </row>
-    <row r="121" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="121" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E121" s="2"/>
     </row>
-    <row r="122" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="122" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E122" s="2"/>
     </row>
-    <row r="123" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="123" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E123" s="2"/>
     </row>
-    <row r="124" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="124" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E124" s="2"/>
     </row>
-    <row r="125" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="125" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E125" s="2"/>
     </row>
-    <row r="126" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="126" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E126" s="2"/>
     </row>
-    <row r="127" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="127" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E127" s="2"/>
     </row>
-    <row r="128" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="128" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E128" s="2"/>
     </row>
-    <row r="129" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="129" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E129" s="2"/>
     </row>
-    <row r="130" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="130" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E130" s="2"/>
     </row>
-    <row r="131" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="131" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E131" s="2"/>
     </row>
-    <row r="132" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="132" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E132" s="2"/>
     </row>
-    <row r="133" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="133" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E133" s="2"/>
     </row>
-    <row r="134" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="134" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E134" s="2"/>
     </row>
-    <row r="135" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="135" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E135" s="2"/>
     </row>
-    <row r="136" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="136" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E136" s="2"/>
     </row>
-    <row r="137" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="137" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E137" s="2"/>
     </row>
-    <row r="138" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="138" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E138" s="2"/>
     </row>
-    <row r="139" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="139" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E139" s="2"/>
     </row>
-    <row r="140" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="140" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E140" s="2"/>
     </row>
-    <row r="141" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="141" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E141" s="2"/>
     </row>
-    <row r="142" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="142" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E142" s="2"/>
     </row>
-    <row r="143" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="143" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E143" s="2"/>
     </row>
-    <row r="144" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="144" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E144" s="2"/>
     </row>
-    <row r="145" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="145" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E145" s="2"/>
     </row>
-    <row r="146" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="146" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E146" s="2"/>
     </row>
-    <row r="147" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="147" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E147" s="2"/>
     </row>
-    <row r="148" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="148" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E148" s="2"/>
     </row>
-    <row r="149" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="149" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E149" s="2"/>
     </row>
-    <row r="150" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="150" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E150" s="2"/>
     </row>
-    <row r="151" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="151" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E151" s="2"/>
     </row>
-    <row r="152" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="152" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E152" s="2"/>
     </row>
-    <row r="153" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="153" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E153" s="2"/>
     </row>
-    <row r="154" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="154" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E154" s="2"/>
     </row>
-    <row r="155" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="155" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E155" s="2"/>
     </row>
-    <row r="156" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="156" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E156" s="2"/>
     </row>
-    <row r="157" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="157" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E157" s="2"/>
     </row>
-    <row r="158" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="158" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E158" s="2"/>
     </row>
-    <row r="159" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="159" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E159" s="2"/>
     </row>
-    <row r="160" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="160" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E160" s="2"/>
     </row>
-    <row r="161" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="161" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E161" s="2"/>
     </row>
-    <row r="162" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="162" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E162" s="2"/>
     </row>
-    <row r="163" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="163" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E163" s="2"/>
     </row>
-    <row r="164" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="164" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E164" s="2"/>
     </row>
-    <row r="165" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="165" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E165" s="2"/>
     </row>
-    <row r="166" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="166" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E166" s="2"/>
     </row>
-    <row r="167" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="167" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E167" s="2"/>
     </row>
-    <row r="168" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="168" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E168" s="2"/>
     </row>
-    <row r="169" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="169" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E169" s="2"/>
     </row>
-    <row r="170" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="170" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E170" s="2"/>
     </row>
-    <row r="171" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="171" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E171" s="2"/>
     </row>
-    <row r="172" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="172" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E172" s="2"/>
     </row>
-    <row r="173" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="173" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E173" s="2"/>
     </row>
-    <row r="174" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="174" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E174" s="2"/>
     </row>
-    <row r="175" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="175" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E175" s="2"/>
     </row>
-    <row r="176" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="176" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E176" s="2"/>
     </row>
-    <row r="177" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="177" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E177" s="2"/>
     </row>
-    <row r="178" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="178" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E178" s="2"/>
     </row>
-    <row r="179" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="179" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E179" s="2"/>
     </row>
-    <row r="180" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="180" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E180" s="2"/>
     </row>
-    <row r="181" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="181" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E181" s="2"/>
     </row>
-    <row r="182" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="182" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E182" s="2"/>
     </row>
-    <row r="183" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="183" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E183" s="2"/>
     </row>
-    <row r="184" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="184" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E184" s="2"/>
     </row>
-    <row r="185" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="185" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E185" s="2"/>
     </row>
-    <row r="186" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="186" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E186" s="2"/>
     </row>
-    <row r="187" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="187" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E187" s="2"/>
     </row>
-    <row r="188" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="188" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E188" s="2"/>
     </row>
-    <row r="189" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="189" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E189" s="2"/>
     </row>
-    <row r="190" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="190" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E190" s="2"/>
     </row>
-    <row r="191" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="191" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E191" s="2"/>
     </row>
-    <row r="192" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="192" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E192" s="2"/>
     </row>
-    <row r="193" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="193" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E193" s="2"/>
     </row>
-    <row r="194" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="194" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E194" s="2"/>
     </row>
-    <row r="195" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="195" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E195" s="2"/>
     </row>
-    <row r="196" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="196" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E196" s="2"/>
     </row>
-    <row r="197" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="197" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E197" s="2"/>
     </row>
-    <row r="198" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="198" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E198" s="2"/>
     </row>
-    <row r="199" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="199" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E199" s="2"/>
     </row>
-    <row r="200" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="200" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E200" s="2"/>
     </row>
-    <row r="201" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="201" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E201" s="2"/>
     </row>
-    <row r="202" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="202" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E202" s="2"/>
     </row>
-    <row r="203" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="203" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E203" s="2"/>
     </row>
-    <row r="204" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="204" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E204" s="2"/>
     </row>
-    <row r="205" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="205" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E205" s="2"/>
     </row>
-    <row r="206" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="206" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E206" s="2"/>
     </row>
-    <row r="207" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="207" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E207" s="2"/>
     </row>
-    <row r="208" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="208" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E208" s="2"/>
     </row>
-    <row r="209" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="209" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E209" s="2"/>
     </row>
-    <row r="210" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="210" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E210" s="2"/>
     </row>
-    <row r="211" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="211" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E211" s="2"/>
     </row>
-    <row r="212" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="212" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E212" s="2"/>
     </row>
-    <row r="213" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="213" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E213" s="2"/>
     </row>
-    <row r="214" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="214" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E214" s="2"/>
     </row>
-    <row r="215" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="215" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E215" s="2"/>
     </row>
-    <row r="216" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="216" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E216" s="2"/>
     </row>
-    <row r="217" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="217" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E217" s="2"/>
     </row>
-    <row r="218" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="218" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E218" s="2"/>
     </row>
-    <row r="219" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="219" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E219" s="2"/>
     </row>
-    <row r="220" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="220" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E220" s="2"/>
     </row>
-    <row r="221" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="221" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E221" s="2"/>
     </row>
-    <row r="222" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="222" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E222" s="2"/>
     </row>
-    <row r="223" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="223" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E223" s="2"/>
     </row>
-    <row r="224" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="224" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E224" s="2"/>
     </row>
-    <row r="225" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="225" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E225" s="2"/>
     </row>
-    <row r="226" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="226" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E226" s="2"/>
     </row>
-    <row r="227" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="227" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E227" s="2"/>
     </row>
-    <row r="228" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="228" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E228" s="2"/>
     </row>
-    <row r="229" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="229" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E229" s="2"/>
     </row>
-    <row r="230" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="230" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E230" s="2"/>
     </row>
-    <row r="231" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="231" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E231" s="2"/>
     </row>
-    <row r="232" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="232" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E232" s="2"/>
     </row>
-    <row r="233" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="233" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E233" s="2"/>
     </row>
-    <row r="234" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="234" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E234" s="2"/>
     </row>
-    <row r="235" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="235" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E235" s="2"/>
     </row>
-    <row r="236" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="236" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E236" s="2"/>
     </row>
-    <row r="237" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="237" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E237" s="2"/>
     </row>
-    <row r="238" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="238" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E238" s="2"/>
     </row>
-    <row r="239" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="239" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E239" s="2"/>
     </row>
-    <row r="240" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="240" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E240" s="2"/>
     </row>
-    <row r="241" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="241" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E241" s="2"/>
     </row>
-    <row r="242" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="242" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E242" s="2"/>
     </row>
-    <row r="243" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="243" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E243" s="2"/>
     </row>
-    <row r="244" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="244" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E244" s="2"/>
     </row>
-    <row r="245" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="245" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E245" s="2"/>
     </row>
-    <row r="246" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="246" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E246" s="2"/>
     </row>
-    <row r="247" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="247" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E247" s="2"/>
     </row>
-    <row r="248" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="248" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E248" s="2"/>
     </row>
-    <row r="249" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="249" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E249" s="2"/>
     </row>
-    <row r="250" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="250" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E250" s="2"/>
     </row>
-    <row r="251" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="251" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E251" s="2"/>
     </row>
-    <row r="252" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="252" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E252" s="2"/>
     </row>
-    <row r="253" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="253" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E253" s="2"/>
     </row>
-    <row r="254" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="254" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E254" s="2"/>
     </row>
-    <row r="255" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="255" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E255" s="2"/>
     </row>
-    <row r="256" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="256" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E256" s="2"/>
     </row>
-    <row r="257" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="257" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E257" s="2"/>
     </row>
-    <row r="258" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="258" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E258" s="2"/>
     </row>
-    <row r="259" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="259" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E259" s="2"/>
     </row>
-    <row r="260" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="260" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E260" s="2"/>
     </row>
-    <row r="261" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="261" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E261" s="2"/>
     </row>
-    <row r="262" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="262" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E262" s="2"/>
     </row>
-    <row r="263" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="263" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E263" s="2"/>
     </row>
-    <row r="264" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="264" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E264" s="2"/>
     </row>
-    <row r="265" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="265" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E265" s="2"/>
     </row>
-    <row r="266" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="266" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E266" s="2"/>
     </row>
-    <row r="267" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="267" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E267" s="2"/>
     </row>
-    <row r="268" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="268" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E268" s="2"/>
     </row>
-    <row r="269" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="269" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E269" s="2"/>
     </row>
-    <row r="270" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="270" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E270" s="2"/>
     </row>
-    <row r="271" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="271" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E271" s="2"/>
     </row>
-    <row r="272" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="272" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E272" s="2"/>
     </row>
-    <row r="273" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="273" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E273" s="2"/>
     </row>
-    <row r="274" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="274" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E274" s="2"/>
     </row>
-    <row r="275" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="275" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E275" s="2"/>
     </row>
-    <row r="276" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="276" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E276" s="2"/>
     </row>
-    <row r="277" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="277" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E277" s="2"/>
     </row>
-    <row r="278" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="278" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E278" s="2"/>
     </row>
-    <row r="279" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="279" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E279" s="2"/>
     </row>
-    <row r="280" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="280" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E280" s="2"/>
     </row>
-    <row r="281" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="281" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E281" s="2"/>
     </row>
-    <row r="282" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="282" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E282" s="2"/>
     </row>
-    <row r="283" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="283" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E283" s="2"/>
     </row>
-    <row r="284" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="284" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E284" s="2"/>
     </row>
-    <row r="285" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="285" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E285" s="2"/>
     </row>
-    <row r="286" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="286" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E286" s="2"/>
     </row>
-    <row r="287" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="287" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E287" s="2"/>
     </row>
-    <row r="288" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="288" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E288" s="2"/>
     </row>
-    <row r="289" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="289" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E289" s="2"/>
     </row>
-    <row r="290" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="290" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E290" s="2"/>
     </row>
-    <row r="291" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="291" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E291" s="2"/>
     </row>
-    <row r="292" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="292" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E292" s="2"/>
     </row>
-    <row r="293" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="293" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E293" s="2"/>
     </row>
-    <row r="294" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="294" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E294" s="2"/>
     </row>
-    <row r="295" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="295" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E295" s="2"/>
     </row>
-    <row r="296" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="296" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E296" s="2"/>
     </row>
-    <row r="297" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="297" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E297" s="2"/>
     </row>
-    <row r="298" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="298" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E298" s="2"/>
     </row>
-    <row r="299" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="299" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E299" s="2"/>
     </row>
-    <row r="300" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="300" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E300" s="2"/>
     </row>
-    <row r="301" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="301" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E301" s="2"/>
     </row>
-    <row r="302" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="302" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E302" s="2"/>
     </row>
-    <row r="303" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="303" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E303" s="2"/>
     </row>
-    <row r="304" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="304" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E304" s="2"/>
     </row>
-    <row r="305" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="305" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E305" s="2"/>
     </row>
-    <row r="306" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="306" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E306" s="2"/>
     </row>
-    <row r="307" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="307" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E307" s="2"/>
     </row>
-    <row r="308" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="308" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E308" s="2"/>
     </row>
-    <row r="309" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="309" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E309" s="2"/>
     </row>
-    <row r="310" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="310" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E310" s="2"/>
     </row>
-    <row r="311" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="311" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E311" s="2"/>
     </row>
-    <row r="312" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="312" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E312" s="2"/>
     </row>
-    <row r="313" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="313" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E313" s="2"/>
     </row>
-    <row r="314" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="314" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E314" s="2"/>
     </row>
-    <row r="315" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="315" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E315" s="2"/>
     </row>
-    <row r="316" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="316" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E316" s="2"/>
     </row>
-    <row r="317" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="317" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E317" s="2"/>
     </row>
-    <row r="318" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="318" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E318" s="2"/>
     </row>
-    <row r="319" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="319" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E319" s="2"/>
     </row>
-    <row r="320" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="320" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E320" s="2"/>
     </row>
-    <row r="321" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="321" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E321" s="2"/>
     </row>
-    <row r="322" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="322" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E322" s="2"/>
     </row>
-    <row r="323" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="323" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E323" s="2"/>
     </row>
-    <row r="324" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="324" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E324" s="2"/>
     </row>
-    <row r="325" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="325" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E325" s="2"/>
     </row>
-    <row r="326" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="326" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E326" s="2"/>
     </row>
-    <row r="327" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="327" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E327" s="2"/>
     </row>
-    <row r="328" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="328" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E328" s="2"/>
     </row>
-    <row r="329" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="329" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E329" s="2"/>
     </row>
-    <row r="330" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="330" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E330" s="2"/>
     </row>
-    <row r="331" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="331" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E331" s="2"/>
     </row>
-    <row r="332" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="332" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E332" s="2"/>
     </row>
-    <row r="333" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="333" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E333" s="2"/>
     </row>
-    <row r="334" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="334" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E334" s="2"/>
     </row>
-    <row r="335" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="335" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E335" s="2"/>
     </row>
-    <row r="336" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="336" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E336" s="2"/>
     </row>
-    <row r="337" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="337" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E337" s="2"/>
     </row>
-    <row r="338" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="338" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E338" s="2"/>
     </row>
-    <row r="339" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="339" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E339" s="2"/>
     </row>
-    <row r="340" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="340" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E340" s="2"/>
     </row>
-    <row r="341" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="341" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E341" s="2"/>
     </row>
-    <row r="342" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="342" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E342" s="2"/>
     </row>
-    <row r="343" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="343" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E343" s="2"/>
     </row>
-    <row r="344" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="344" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E344" s="2"/>
     </row>
-    <row r="345" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="345" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E345" s="2"/>
     </row>
-    <row r="346" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="346" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E346" s="2"/>
     </row>
-    <row r="347" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="347" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E347" s="2"/>
     </row>
-    <row r="348" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="348" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E348" s="2"/>
     </row>
-    <row r="349" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="349" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E349" s="2"/>
     </row>
-    <row r="350" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="350" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E350" s="2"/>
     </row>
-    <row r="351" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="351" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E351" s="2"/>
     </row>
-    <row r="352" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="352" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E352" s="2"/>
     </row>
-    <row r="353" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="353" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E353" s="2"/>
     </row>
-    <row r="354" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="354" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E354" s="2"/>
     </row>
-    <row r="355" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="355" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E355" s="2"/>
     </row>
-    <row r="356" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="356" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E356" s="2"/>
     </row>
-    <row r="357" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="357" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E357" s="2"/>
     </row>
-    <row r="358" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="358" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E358" s="2"/>
     </row>
-    <row r="359" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="359" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E359" s="2"/>
     </row>
-    <row r="360" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="360" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E360" s="2"/>
     </row>
-    <row r="361" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="361" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E361" s="2"/>
     </row>
-    <row r="362" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="362" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E362" s="2"/>
     </row>
-    <row r="363" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="363" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E363" s="2"/>
     </row>
-    <row r="364" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="364" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E364" s="2"/>
     </row>
-    <row r="365" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="365" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E365" s="2"/>
     </row>
-    <row r="366" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="366" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E366" s="2"/>
     </row>
-    <row r="367" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="367" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E367" s="2"/>
     </row>
-    <row r="368" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="368" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E368" s="2"/>
     </row>
-    <row r="369" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="369" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E369" s="2"/>
     </row>
-    <row r="370" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="370" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E370" s="2"/>
     </row>
-    <row r="371" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="371" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E371" s="2"/>
     </row>
-    <row r="372" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="372" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E372" s="2"/>
     </row>
-    <row r="373" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="373" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E373" s="2"/>
     </row>
-    <row r="374" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="374" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E374" s="2"/>
     </row>
-    <row r="375" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="375" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E375" s="2"/>
     </row>
-    <row r="376" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="376" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E376" s="2"/>
     </row>
-    <row r="377" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="377" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E377" s="2"/>
     </row>
-    <row r="378" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="378" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E378" s="2"/>
     </row>
-    <row r="379" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="379" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E379" s="2"/>
     </row>
-    <row r="380" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="380" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E380" s="2"/>
     </row>
-    <row r="381" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="381" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E381" s="2"/>
     </row>
-    <row r="382" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="382" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E382" s="2"/>
     </row>
-    <row r="383" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="383" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E383" s="2"/>
     </row>
-    <row r="384" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="384" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E384" s="2"/>
     </row>
-    <row r="385" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="385" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E385" s="2"/>
     </row>
-    <row r="386" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="386" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E386" s="2"/>
     </row>
-    <row r="387" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="387" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E387" s="2"/>
     </row>
-    <row r="388" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="388" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E388" s="2"/>
     </row>
-    <row r="389" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="389" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E389" s="2"/>
     </row>
-    <row r="390" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="390" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E390" s="2"/>
     </row>
-    <row r="391" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="391" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E391" s="2"/>
     </row>
-    <row r="392" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="392" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E392" s="2"/>
     </row>
-    <row r="393" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="393" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E393" s="2"/>
     </row>
-    <row r="394" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="394" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E394" s="2"/>
     </row>
-    <row r="395" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="395" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E395" s="2"/>
     </row>
-    <row r="396" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="396" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E396" s="2"/>
     </row>
-    <row r="397" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="397" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E397" s="2"/>
     </row>
-    <row r="398" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="398" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E398" s="2"/>
     </row>
-    <row r="399" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="399" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E399" s="2"/>
     </row>
-    <row r="400" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="400" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E400" s="2"/>
     </row>
-    <row r="401" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="401" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E401" s="2"/>
     </row>
-    <row r="402" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="402" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E402" s="2"/>
     </row>
-    <row r="403" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="403" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E403" s="2"/>
     </row>
-    <row r="404" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="404" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E404" s="2"/>
     </row>
-    <row r="405" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="405" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E405" s="2"/>
     </row>
-    <row r="406" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="406" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E406" s="2"/>
     </row>
-    <row r="407" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="407" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E407" s="2"/>
     </row>
-    <row r="408" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="408" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E408" s="2"/>
     </row>
-    <row r="409" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="409" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E409" s="2"/>
     </row>
-    <row r="410" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="410" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E410" s="2"/>
     </row>
-    <row r="411" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="411" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E411" s="2"/>
     </row>
-    <row r="412" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="412" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E412" s="2"/>
     </row>
-    <row r="413" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="413" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E413" s="2"/>
     </row>
-    <row r="414" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="414" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E414" s="2"/>
     </row>
-    <row r="415" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="415" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E415" s="2"/>
     </row>
-    <row r="416" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="416" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E416" s="2"/>
     </row>
-    <row r="417" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="417" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E417" s="2"/>
     </row>
-    <row r="418" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="418" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E418" s="2"/>
     </row>
-    <row r="419" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="419" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E419" s="2"/>
     </row>
-    <row r="420" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="420" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E420" s="2"/>
     </row>
-    <row r="421" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="421" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E421" s="2"/>
     </row>
-    <row r="422" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="422" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E422" s="2"/>
     </row>
-    <row r="423" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="423" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E423" s="2"/>
     </row>
-    <row r="424" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="424" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E424" s="2"/>
     </row>
-    <row r="425" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="425" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E425" s="2"/>
     </row>
-    <row r="426" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="426" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E426" s="2"/>
     </row>
-    <row r="427" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="427" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E427" s="2"/>
     </row>
-    <row r="428" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="428" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E428" s="2"/>
     </row>
-    <row r="429" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="429" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E429" s="2"/>
     </row>
-    <row r="430" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="430" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E430" s="2"/>
     </row>
-    <row r="431" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="431" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E431" s="2"/>
     </row>
-    <row r="432" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="432" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E432" s="2"/>
     </row>
-    <row r="433" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="433" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E433" s="2"/>
     </row>
-    <row r="434" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="434" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E434" s="2"/>
     </row>
-    <row r="435" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="435" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E435" s="2"/>
     </row>
-    <row r="436" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="436" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E436" s="2"/>
     </row>
-    <row r="437" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="437" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E437" s="2"/>
     </row>
-    <row r="438" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="438" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E438" s="2"/>
     </row>
-    <row r="439" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="439" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E439" s="2"/>
     </row>
-    <row r="440" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="440" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E440" s="2"/>
     </row>
-    <row r="441" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="441" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E441" s="2"/>
     </row>
-    <row r="442" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="442" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E442" s="2"/>
     </row>
-    <row r="443" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="443" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E443" s="2"/>
     </row>
-    <row r="444" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="444" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E444" s="2"/>
     </row>
-    <row r="445" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="445" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E445" s="2"/>
     </row>
-    <row r="446" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="446" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E446" s="2"/>
     </row>
-    <row r="447" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="447" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E447" s="2"/>
     </row>
-    <row r="448" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="448" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E448" s="2"/>
     </row>
-    <row r="449" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="449" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E449" s="2"/>
     </row>
-    <row r="450" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="450" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E450" s="2"/>
     </row>
-    <row r="451" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="451" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E451" s="2"/>
     </row>
-    <row r="452" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="452" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E452" s="2"/>
     </row>
-    <row r="453" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="453" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E453" s="2"/>
     </row>
-    <row r="454" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="454" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E454" s="2"/>
     </row>
-    <row r="455" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="455" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E455" s="2"/>
     </row>
-    <row r="456" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="456" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E456" s="2"/>
     </row>
-    <row r="457" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="457" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E457" s="2"/>
     </row>
-    <row r="458" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="458" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E458" s="2"/>
     </row>
-    <row r="459" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="459" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E459" s="2"/>
     </row>
-    <row r="460" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="460" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E460" s="2"/>
     </row>
-    <row r="461" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="461" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E461" s="2"/>
     </row>
-    <row r="462" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="462" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E462" s="2"/>
     </row>
-    <row r="463" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="463" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E463" s="2"/>
     </row>
-    <row r="464" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="464" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E464" s="2"/>
     </row>
-    <row r="465" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="465" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E465" s="2"/>
     </row>
-    <row r="466" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="466" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E466" s="2"/>
     </row>
-    <row r="467" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="467" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E467" s="2"/>
     </row>
-    <row r="468" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="468" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E468" s="2"/>
     </row>
-    <row r="469" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="469" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E469" s="2"/>
     </row>
-    <row r="470" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="470" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E470" s="2"/>
     </row>
-    <row r="471" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="471" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E471" s="2"/>
     </row>
-    <row r="472" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="472" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E472" s="2"/>
     </row>
-    <row r="473" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="473" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E473" s="2"/>
     </row>
-    <row r="474" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="474" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E474" s="2"/>
     </row>
-    <row r="475" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="475" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E475" s="2"/>
     </row>
-    <row r="476" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="476" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E476" s="2"/>
     </row>
-    <row r="477" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="477" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E477" s="2"/>
     </row>
-    <row r="478" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="478" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E478" s="2"/>
     </row>
-    <row r="479" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="479" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E479" s="2"/>
     </row>
-    <row r="480" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="480" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E480" s="2"/>
     </row>
-    <row r="481" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="481" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E481" s="2"/>
     </row>
-    <row r="482" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="482" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E482" s="2"/>
     </row>
-    <row r="483" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="483" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E483" s="2"/>
     </row>
-    <row r="484" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="484" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E484" s="2"/>
     </row>
-    <row r="485" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="485" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E485" s="2"/>
     </row>
-    <row r="486" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="486" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E486" s="2"/>
     </row>
-    <row r="487" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="487" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E487" s="2"/>
     </row>
-    <row r="488" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="488" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E488" s="2"/>
     </row>
-    <row r="489" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="489" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E489" s="2"/>
     </row>
-    <row r="490" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="490" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E490" s="2"/>
     </row>
-    <row r="491" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="491" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E491" s="2"/>
     </row>
-    <row r="492" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="492" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E492" s="2"/>
     </row>
-    <row r="493" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="493" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E493" s="2"/>
     </row>
-    <row r="494" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="494" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E494" s="2"/>
     </row>
-    <row r="495" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="495" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E495" s="2"/>
     </row>
-    <row r="496" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="496" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E496" s="2"/>
     </row>
-    <row r="497" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="497" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E497" s="2"/>
     </row>
-    <row r="498" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="498" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E498" s="2"/>
     </row>
-    <row r="499" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="499" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E499" s="2"/>
     </row>
-    <row r="500" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="500" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E500" s="2"/>
     </row>
-    <row r="501" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="501" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E501" s="2"/>
     </row>
-    <row r="502" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="502" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E502" s="2"/>
     </row>
-    <row r="503" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="503" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E503" s="2"/>
     </row>
-    <row r="504" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="504" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E504" s="2"/>
     </row>
-    <row r="505" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="505" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E505" s="2"/>
     </row>
-    <row r="506" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="506" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E506" s="2"/>
     </row>
-    <row r="507" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="507" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E507" s="2"/>
     </row>
-    <row r="508" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="508" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E508" s="2"/>
     </row>
-    <row r="509" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="509" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E509" s="2"/>
     </row>
-    <row r="510" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="510" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E510" s="2"/>
     </row>
-    <row r="511" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="511" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E511" s="2"/>
     </row>
-    <row r="512" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="512" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E512" s="2"/>
     </row>
-    <row r="513" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="513" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E513" s="2"/>
     </row>
-    <row r="514" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="514" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E514" s="2"/>
     </row>
-    <row r="515" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="515" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E515" s="2"/>
     </row>
-    <row r="516" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="516" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E516" s="2"/>
     </row>
-    <row r="517" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="517" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E517" s="2"/>
     </row>
-    <row r="518" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="518" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E518" s="2"/>
     </row>
-    <row r="519" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="519" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E519" s="2"/>
     </row>
-    <row r="520" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="520" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E520" s="2"/>
     </row>
-    <row r="521" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="521" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E521" s="2"/>
     </row>
-    <row r="522" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="522" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E522" s="2"/>
     </row>
-    <row r="523" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="523" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E523" s="2"/>
     </row>
-    <row r="524" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="524" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E524" s="2"/>
     </row>
-    <row r="525" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="525" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E525" s="2"/>
     </row>
-    <row r="526" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="526" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E526" s="2"/>
     </row>
-    <row r="527" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="527" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E527" s="2"/>
     </row>
-    <row r="528" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="528" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E528" s="2"/>
     </row>
-    <row r="529" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="529" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E529" s="2"/>
     </row>
-    <row r="530" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="530" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E530" s="2"/>
     </row>
-    <row r="531" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="531" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E531" s="2"/>
     </row>
-    <row r="532" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="532" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E532" s="2"/>
     </row>
-    <row r="533" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="533" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E533" s="2"/>
     </row>
-    <row r="534" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="534" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E534" s="2"/>
     </row>
-    <row r="535" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="535" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E535" s="2"/>
     </row>
-    <row r="536" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="536" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E536" s="2"/>
     </row>
-    <row r="537" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="537" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E537" s="2"/>
     </row>
-    <row r="538" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="538" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E538" s="2"/>
     </row>
-    <row r="539" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="539" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E539" s="2"/>
     </row>
-    <row r="540" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="540" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E540" s="2"/>
     </row>
-    <row r="541" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="541" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E541" s="2"/>
     </row>
-    <row r="542" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="542" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E542" s="2"/>
     </row>
-    <row r="543" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="543" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E543" s="2"/>
     </row>
-    <row r="544" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="544" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E544" s="2"/>
     </row>
-    <row r="545" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="545" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E545" s="2"/>
     </row>
-    <row r="546" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="546" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E546" s="2"/>
     </row>
-    <row r="547" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="547" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E547" s="2"/>
     </row>
-    <row r="548" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="548" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E548" s="2"/>
     </row>
-    <row r="549" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="549" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E549" s="2"/>
     </row>
-    <row r="550" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="550" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E550" s="2"/>
     </row>
-    <row r="551" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="551" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E551" s="2"/>
     </row>
-    <row r="552" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="552" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E552" s="2"/>
     </row>
-    <row r="553" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="553" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E553" s="2"/>
     </row>
-    <row r="554" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="554" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E554" s="2"/>
     </row>
-    <row r="555" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="555" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E555" s="2"/>
     </row>
-    <row r="556" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="556" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E556" s="2"/>
     </row>
-    <row r="557" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="557" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E557" s="2"/>
     </row>
-    <row r="558" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="558" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E558" s="2"/>
     </row>
-    <row r="559" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="559" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E559" s="2"/>
     </row>
-    <row r="560" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="560" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E560" s="2"/>
     </row>
-    <row r="561" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="561" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E561" s="2"/>
     </row>
-    <row r="562" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="562" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E562" s="2"/>
     </row>
-    <row r="563" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="563" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E563" s="2"/>
     </row>
-    <row r="564" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="564" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E564" s="2"/>
     </row>
-    <row r="565" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="565" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E565" s="2"/>
     </row>
-    <row r="566" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="566" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E566" s="2"/>
     </row>
-    <row r="567" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="567" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E567" s="2"/>
     </row>
-    <row r="568" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="568" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E568" s="2"/>
     </row>
-    <row r="569" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="569" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E569" s="2"/>
     </row>
-    <row r="570" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="570" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E570" s="2"/>
     </row>
-    <row r="571" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="571" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E571" s="2"/>
     </row>
-    <row r="572" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="572" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E572" s="2"/>
     </row>
-    <row r="573" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="573" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E573" s="2"/>
     </row>
-    <row r="574" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="574" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E574" s="2"/>
     </row>
-    <row r="575" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="575" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E575" s="2"/>
     </row>
-    <row r="576" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="576" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E576" s="2"/>
     </row>
-    <row r="577" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="577" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E577" s="2"/>
     </row>
-    <row r="578" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="578" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E578" s="2"/>
     </row>
-    <row r="579" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="579" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E579" s="2"/>
     </row>
-    <row r="580" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="580" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E580" s="2"/>
     </row>
-    <row r="581" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="581" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E581" s="2"/>
     </row>
-    <row r="582" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="582" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E582" s="2"/>
     </row>
-    <row r="583" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="583" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E583" s="2"/>
     </row>
-    <row r="584" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="584" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E584" s="2"/>
     </row>
-    <row r="585" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="585" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E585" s="2"/>
     </row>
-    <row r="586" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="586" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E586" s="2"/>
     </row>
-    <row r="587" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="587" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E587" s="2"/>
     </row>
-    <row r="588" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="588" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E588" s="2"/>
     </row>
-    <row r="589" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="589" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E589" s="2"/>
     </row>
-    <row r="590" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="590" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E590" s="2"/>
     </row>
-    <row r="591" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="591" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E591" s="2"/>
     </row>
-    <row r="592" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="592" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E592" s="2"/>
     </row>
-    <row r="593" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="593" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E593" s="2"/>
     </row>
-    <row r="594" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="594" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E594" s="2"/>
     </row>
-    <row r="595" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="595" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E595" s="2"/>
     </row>
-    <row r="596" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="596" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E596" s="2"/>
     </row>
-    <row r="597" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="597" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E597" s="2"/>
     </row>
-    <row r="598" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="598" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E598" s="2"/>
     </row>
-    <row r="599" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="599" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E599" s="2"/>
     </row>
-    <row r="600" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="600" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E600" s="2"/>
     </row>
-    <row r="601" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="601" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E601" s="2"/>
     </row>
-    <row r="602" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="602" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E602" s="2"/>
     </row>
-    <row r="603" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="603" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E603" s="2"/>
     </row>
-    <row r="604" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="604" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E604" s="2"/>
     </row>
-    <row r="605" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="605" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E605" s="2"/>
     </row>
-    <row r="606" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="606" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E606" s="2"/>
     </row>
-    <row r="607" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="607" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E607" s="2"/>
     </row>
-    <row r="608" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="608" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E608" s="2"/>
     </row>
-    <row r="609" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="609" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E609" s="2"/>
     </row>
-    <row r="610" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="610" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E610" s="2"/>
     </row>
-    <row r="611" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="611" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E611" s="2"/>
     </row>
-    <row r="612" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="612" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E612" s="2"/>
     </row>
-    <row r="613" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="613" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E613" s="2"/>
     </row>
-    <row r="614" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="614" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E614" s="2"/>
     </row>
-    <row r="615" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="615" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E615" s="2"/>
     </row>
-    <row r="616" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="616" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E616" s="2"/>
     </row>
-    <row r="617" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="617" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E617" s="2"/>
     </row>
-    <row r="618" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="618" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E618" s="2"/>
     </row>
-    <row r="619" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="619" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E619" s="2"/>
     </row>
-    <row r="620" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="620" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E620" s="2"/>
     </row>
-    <row r="621" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="621" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E621" s="2"/>
     </row>
-    <row r="622" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="622" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E622" s="2"/>
     </row>
-    <row r="623" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="623" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E623" s="2"/>
     </row>
-    <row r="624" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="624" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E624" s="2"/>
     </row>
-    <row r="625" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="625" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E625" s="2"/>
     </row>
-    <row r="626" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="626" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E626" s="2"/>
     </row>
-    <row r="627" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="627" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E627" s="2"/>
     </row>
-    <row r="628" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="628" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E628" s="2"/>
     </row>
-    <row r="629" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="629" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E629" s="2"/>
     </row>
-    <row r="630" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="630" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E630" s="2"/>
     </row>
-    <row r="631" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="631" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E631" s="2"/>
     </row>
-    <row r="632" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="632" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E632" s="2"/>
     </row>
-    <row r="633" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="633" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E633" s="2"/>
     </row>
-    <row r="634" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="634" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E634" s="2"/>
     </row>
-    <row r="635" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="635" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E635" s="2"/>
     </row>
-    <row r="636" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="636" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E636" s="2"/>
     </row>
-    <row r="637" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="637" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E637" s="2"/>
     </row>
-    <row r="638" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="638" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E638" s="2"/>
     </row>
-    <row r="639" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="639" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E639" s="2"/>
     </row>
-    <row r="640" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="640" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E640" s="2"/>
     </row>
-    <row r="641" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="641" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E641" s="2"/>
     </row>
-    <row r="642" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="642" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E642" s="2"/>
     </row>
-    <row r="643" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="643" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E643" s="2"/>
     </row>
-    <row r="644" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="644" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E644" s="2"/>
     </row>
-    <row r="645" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="645" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E645" s="2"/>
     </row>
-    <row r="646" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="646" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E646" s="2"/>
     </row>
-    <row r="647" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="647" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E647" s="2"/>
     </row>
-    <row r="648" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="648" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E648" s="2"/>
     </row>
-    <row r="649" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="649" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E649" s="2"/>
     </row>
-    <row r="650" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="650" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E650" s="2"/>
     </row>
-    <row r="651" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="651" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E651" s="2"/>
     </row>
-    <row r="652" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="652" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E652" s="2"/>
     </row>
-    <row r="653" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="653" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E653" s="2"/>
     </row>
-    <row r="654" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="654" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E654" s="2"/>
     </row>
-    <row r="655" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="655" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E655" s="2"/>
     </row>
-    <row r="656" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="656" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E656" s="2"/>
     </row>
-    <row r="657" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="657" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E657" s="2"/>
     </row>
-    <row r="658" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="658" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E658" s="2"/>
     </row>
-    <row r="659" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="659" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E659" s="2"/>
     </row>
-    <row r="660" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="660" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E660" s="2"/>
     </row>
-    <row r="661" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="661" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E661" s="2"/>
     </row>
-    <row r="662" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="662" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E662" s="2"/>
     </row>
-    <row r="663" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="663" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E663" s="2"/>
     </row>
-    <row r="664" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="664" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E664" s="2"/>
     </row>
-    <row r="665" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="665" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E665" s="2"/>
     </row>
-    <row r="666" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="666" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E666" s="2"/>
     </row>
-    <row r="667" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="667" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E667" s="2"/>
     </row>
-    <row r="668" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="668" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E668" s="2"/>
     </row>
-    <row r="669" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="669" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E669" s="2"/>
     </row>
-    <row r="670" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="670" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E670" s="2"/>
     </row>
-    <row r="671" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="671" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E671" s="2"/>
     </row>
-    <row r="672" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="672" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E672" s="2"/>
     </row>
-    <row r="673" spans="5:5" x14ac:dyDescent="0.15">
+    <row r="673" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E673" s="2"/>
     </row>
   </sheetData>
@@ -2834,9 +2830,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
